--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEEC7C7-6A0F-495D-84E3-E5FE3A2F0A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1BA114-D83E-41C4-854F-42BD87003A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,22 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>RECUSAS MDS 27.10.2025</t>
-  </si>
-  <si>
-    <t>135080039</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 27.10.2025</t>
-  </si>
-  <si>
-    <t>135084357</t>
-  </si>
-  <si>
-    <t>135099547</t>
-  </si>
-  <si>
-    <t>134998500</t>
+    <t>135068836</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 28.10.2025</t>
+  </si>
+  <si>
+    <t>134982699</t>
+  </si>
+  <si>
+    <t>135140926</t>
+  </si>
+  <si>
+    <t>135090961</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 28.10.2025</t>
   </si>
 </sst>
 </file>
@@ -497,33 +497,34 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -531,16 +532,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -548,16 +549,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1BA114-D83E-41C4-854F-42BD87003A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A790A2E5-54F4-4E89-BD2C-386C7D7F4C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>135068836</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 28.10.2025</t>
-  </si>
-  <si>
-    <t>134982699</t>
-  </si>
-  <si>
-    <t>135140926</t>
-  </si>
-  <si>
-    <t>135090961</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 28.10.2025</t>
+    <t>134973744</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 29.10.2025</t>
+  </si>
+  <si>
+    <t>134961939</t>
+  </si>
+  <si>
+    <t>888211744</t>
+  </si>
+  <si>
+    <t>888211746</t>
+  </si>
+  <si>
+    <t>888211740</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 29.10.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -524,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -541,7 +544,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -558,9 +561,26 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -578,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A790A2E5-54F4-4E89-BD2C-386C7D7F4C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77701A3-1E95-40AA-A77D-2CFBA8D84A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,25 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>134973744</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 29.10.2025</t>
-  </si>
-  <si>
-    <t>134961939</t>
-  </si>
-  <si>
-    <t>888211744</t>
-  </si>
-  <si>
-    <t>888211746</t>
-  </si>
-  <si>
-    <t>888211740</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 29.10.2025</t>
+    <t>135105129</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 30.10.2025</t>
+  </si>
+  <si>
+    <t>135153660</t>
+  </si>
+  <si>
+    <t>135153391</t>
+  </si>
+  <si>
+    <t>134996615</t>
+  </si>
+  <si>
+    <t>134998943</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 30.10.2025</t>
   </si>
 </sst>
 </file>
@@ -598,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77701A3-1E95-40AA-A77D-2CFBA8D84A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53657212-2D6E-4CB9-A413-CDDE92C62F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,40 @@
     <t>971</t>
   </si>
   <si>
-    <t>135105129</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 30.10.2025</t>
-  </si>
-  <si>
-    <t>135153660</t>
-  </si>
-  <si>
-    <t>135153391</t>
-  </si>
-  <si>
-    <t>134996615</t>
-  </si>
-  <si>
-    <t>134998943</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 30.10.2025</t>
+    <t>888209392</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 02.11.2025</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 02.11.2025</t>
+  </si>
+  <si>
+    <t>135007850</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 31.10.2025</t>
+  </si>
+  <si>
+    <t>135113627</t>
+  </si>
+  <si>
+    <t>135131753</t>
+  </si>
+  <si>
+    <t>135170058</t>
+  </si>
+  <si>
+    <t>135177229</t>
+  </si>
+  <si>
+    <t>135008617</t>
+  </si>
+  <si>
+    <t>135185813</t>
+  </si>
+  <si>
+    <t>RECUSAS MDS 31.10.2025</t>
   </si>
 </sst>
 </file>
@@ -468,7 +483,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -518,16 +533,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -535,16 +550,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -552,16 +567,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -569,18 +584,69 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53657212-2D6E-4CB9-A413-CDDE92C62F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270EF608-287F-457A-A869-AA8DE6AEB6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,40 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>888209392</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 02.11.2025</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 02.11.2025</t>
-  </si>
-  <si>
-    <t>135007850</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 31.10.2025</t>
-  </si>
-  <si>
-    <t>135113627</t>
-  </si>
-  <si>
-    <t>135131753</t>
-  </si>
-  <si>
-    <t>135170058</t>
-  </si>
-  <si>
-    <t>135177229</t>
-  </si>
-  <si>
-    <t>135008617</t>
-  </si>
-  <si>
-    <t>135185813</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 31.10.2025</t>
+    <t>135098607</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 03.11.2025</t>
+  </si>
+  <si>
+    <t>135150398</t>
+  </si>
+  <si>
+    <t>135197954</t>
+  </si>
+  <si>
+    <t>135119660</t>
+  </si>
+  <si>
+    <t>Recusa MDS 03.11.2025</t>
   </si>
 </sst>
 </file>
@@ -483,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -524,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -533,16 +515,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -550,16 +532,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -567,86 +549,18 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -664,31 +578,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270EF608-287F-457A-A869-AA8DE6AEB6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E96C9B-EDFA-45F3-A68E-CD28A201233E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,13 @@
     <t>971</t>
   </si>
   <si>
-    <t>135098607</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 03.11.2025</t>
-  </si>
-  <si>
-    <t>135150398</t>
-  </si>
-  <si>
-    <t>135197954</t>
-  </si>
-  <si>
-    <t>135119660</t>
-  </si>
-  <si>
-    <t>Recusa MDS 03.11.2025</t>
+    <t>135117755</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 04.11.2025</t>
+  </si>
+  <si>
+    <t>Recusa MDS 04.11.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +456,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,63 +497,12 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -578,31 +518,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E96C9B-EDFA-45F3-A68E-CD28A201233E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838E2F16-3EC3-452F-A6FB-A4FCB18B72EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>135117755</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 04.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa MDS 04.11.2025</t>
+    <t>135258054</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 05.11.2025</t>
+  </si>
+  <si>
+    <t>135258591</t>
+  </si>
+  <si>
+    <t>135131175</t>
+  </si>
+  <si>
+    <t>135156221</t>
+  </si>
+  <si>
+    <t>130953407</t>
+  </si>
+  <si>
+    <t>135090653</t>
+  </si>
+  <si>
+    <t>Recusa MDS 05.11.25</t>
   </si>
 </sst>
 </file>
@@ -456,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,12 +512,97 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -518,31 +618,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838E2F16-3EC3-452F-A6FB-A4FCB18B72EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E0B5E7-E3CA-4351-9DD6-F9A21E6B36EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>135258054</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 05.11.2025</t>
-  </si>
-  <si>
-    <t>135258591</t>
-  </si>
-  <si>
-    <t>135131175</t>
-  </si>
-  <si>
-    <t>135156221</t>
-  </si>
-  <si>
     <t>130953407</t>
   </si>
   <si>
     <t>135090653</t>
   </si>
   <si>
-    <t>Recusa MDS 05.11.25</t>
+    <t>135152805</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 06.11.2025</t>
+  </si>
+  <si>
+    <t>135163254</t>
+  </si>
+  <si>
+    <t>Recusa MDS 06.11.25</t>
   </si>
 </sst>
 </file>
@@ -471,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,16 +497,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,16 +515,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -538,16 +532,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -561,46 +555,12 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -618,31 +578,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E0B5E7-E3CA-4351-9DD6-F9A21E6B36EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD0AE70-0B4A-403D-BA97-5E603F00F6EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>130953407</t>
-  </si>
-  <si>
-    <t>135090653</t>
-  </si>
-  <si>
-    <t>135152805</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 06.11.2025</t>
-  </si>
-  <si>
-    <t>135163254</t>
-  </si>
-  <si>
-    <t>Recusa MDS 06.11.25</t>
+    <t>135211190</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 07.11.2025</t>
+  </si>
+  <si>
+    <t>135274914</t>
+  </si>
+  <si>
+    <t>135275757</t>
+  </si>
+  <si>
+    <t>Recusa MDS 07.11.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,16 +494,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -515,16 +512,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -532,35 +529,18 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -578,31 +558,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD0AE70-0B4A-403D-BA97-5E603F00F6EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A0F515-506C-49B2-A25D-29350E1A5AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>135211190</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 07.11.2025</t>
-  </si>
-  <si>
-    <t>135274914</t>
-  </si>
-  <si>
-    <t>135275757</t>
-  </si>
-  <si>
-    <t>Recusa MDS 07.11.2025</t>
+    <t>135188484</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 10.11.2025</t>
+  </si>
+  <si>
+    <t>135307188</t>
+  </si>
+  <si>
+    <t>135293903</t>
+  </si>
+  <si>
+    <t>888210193</t>
+  </si>
+  <si>
+    <t>135189634</t>
+  </si>
+  <si>
+    <t>131185404</t>
+  </si>
+  <si>
+    <t>135329368</t>
+  </si>
+  <si>
+    <t>135151279</t>
+  </si>
+  <si>
+    <t>Recusa MDS 10.11.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,7 +536,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -538,9 +553,94 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -558,31 +658,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A0F515-506C-49B2-A25D-29350E1A5AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E06F76A-3020-4C73-82D2-01615AC41A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="25">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,55 @@
     <t>971</t>
   </si>
   <si>
-    <t>135188484</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 10.11.2025</t>
-  </si>
-  <si>
-    <t>135307188</t>
-  </si>
-  <si>
-    <t>135293903</t>
-  </si>
-  <si>
-    <t>888210193</t>
-  </si>
-  <si>
-    <t>135189634</t>
-  </si>
-  <si>
-    <t>131185404</t>
-  </si>
-  <si>
-    <t>135329368</t>
-  </si>
-  <si>
-    <t>135151279</t>
-  </si>
-  <si>
-    <t>Recusa MDS 10.11.2025</t>
+    <t>135336315</t>
+  </si>
+  <si>
+    <t>Bloqueios Honda 11/11/2025</t>
+  </si>
+  <si>
+    <t>135336344</t>
+  </si>
+  <si>
+    <t>135338935</t>
+  </si>
+  <si>
+    <t>135341777</t>
+  </si>
+  <si>
+    <t>135344162</t>
+  </si>
+  <si>
+    <t>135349787</t>
+  </si>
+  <si>
+    <t>135351227</t>
+  </si>
+  <si>
+    <t>135351911</t>
+  </si>
+  <si>
+    <t>135349683</t>
+  </si>
+  <si>
+    <t>135335834</t>
+  </si>
+  <si>
+    <t>135336776</t>
+  </si>
+  <si>
+    <t>135337444</t>
+  </si>
+  <si>
+    <t>135340093</t>
+  </si>
+  <si>
+    <t>135340216</t>
+  </si>
+  <si>
+    <t>135349919</t>
+  </si>
+  <si>
+    <t>Recusa MDS 11.11.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +498,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +539,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -536,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -553,7 +574,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -570,7 +591,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -587,7 +608,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -604,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -621,7 +642,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -638,9 +659,128 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -658,31 +798,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E06F76A-3020-4C73-82D2-01615AC41A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C704CD0F-84DD-4845-B094-5673822D63DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,55 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>135336315</t>
-  </si>
-  <si>
-    <t>Bloqueios Honda 11/11/2025</t>
-  </si>
-  <si>
-    <t>135336344</t>
-  </si>
-  <si>
-    <t>135338935</t>
-  </si>
-  <si>
-    <t>135341777</t>
-  </si>
-  <si>
-    <t>135344162</t>
-  </si>
-  <si>
-    <t>135349787</t>
-  </si>
-  <si>
-    <t>135351227</t>
-  </si>
-  <si>
-    <t>135351911</t>
-  </si>
-  <si>
-    <t>135349683</t>
-  </si>
-  <si>
-    <t>135335834</t>
-  </si>
-  <si>
-    <t>135336776</t>
-  </si>
-  <si>
-    <t>135337444</t>
-  </si>
-  <si>
-    <t>135340093</t>
-  </si>
-  <si>
-    <t>135340216</t>
-  </si>
-  <si>
-    <t>135349919</t>
-  </si>
-  <si>
-    <t>Recusa MDS 11.11.2025</t>
+    <t>135183638</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 12.11.2025</t>
+  </si>
+  <si>
+    <t>135264725</t>
+  </si>
+  <si>
+    <t>135296682</t>
+  </si>
+  <si>
+    <t>135366994</t>
+  </si>
+  <si>
+    <t>Recusa MDS 12.11.2025</t>
   </si>
 </sst>
 </file>
@@ -498,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -539,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -557,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -574,7 +541,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -591,196 +558,9 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -798,31 +578,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C704CD0F-84DD-4845-B094-5673822D63DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5A9715-4170-46F7-B154-4D571E91AB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>135183638</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 12.11.2025</t>
-  </si>
-  <si>
-    <t>135264725</t>
-  </si>
-  <si>
-    <t>135296682</t>
-  </si>
-  <si>
-    <t>135366994</t>
-  </si>
-  <si>
-    <t>Recusa MDS 12.11.2025</t>
+    <t>Recusa MDS 14.11.2025</t>
+  </si>
+  <si>
+    <t>135264703</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 14.11.2025</t>
+  </si>
+  <si>
+    <t>135251991</t>
+  </si>
+  <si>
+    <t>135382042</t>
+  </si>
+  <si>
+    <t>135195953</t>
+  </si>
+  <si>
+    <t>135392635</t>
   </si>
 </sst>
 </file>
@@ -465,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,16 +500,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -515,16 +518,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -532,16 +535,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -549,18 +552,35 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -578,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5A9715-4170-46F7-B154-4D571E91AB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0321EBC-E042-4D6B-A7F3-27599E3169F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,22 @@
     <t>971</t>
   </si>
   <si>
+    <t>130927862</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 15.11.2025</t>
+  </si>
+  <si>
+    <t>Recusa MDS 15.11.2025</t>
+  </si>
+  <si>
+    <t>135244174</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 14.11.2025</t>
+  </si>
+  <si>
     <t>Recusa MDS 14.11.2025</t>
-  </si>
-  <si>
-    <t>135264703</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 14.11.2025</t>
-  </si>
-  <si>
-    <t>135251991</t>
-  </si>
-  <si>
-    <t>135382042</t>
-  </si>
-  <si>
-    <t>135195953</t>
-  </si>
-  <si>
-    <t>135392635</t>
   </si>
 </sst>
 </file>
@@ -468,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,16 +497,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -524,63 +521,12 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -598,31 +544,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0321EBC-E042-4D6B-A7F3-27599E3169F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4387B9-611E-4E0B-B969-A46739B44B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>130927862</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 15.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa MDS 15.11.2025</t>
-  </si>
-  <si>
-    <t>135244174</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 14.11.2025</t>
-  </si>
-  <si>
-    <t>Recusa MDS 14.11.2025</t>
+    <t>135346571</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 17.11.2025</t>
+  </si>
+  <si>
+    <t>135361779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECUSAS MDS 17.11.2025 </t>
   </si>
 </sst>
 </file>
@@ -506,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -515,16 +509,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -544,31 +538,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4387B9-611E-4E0B-B969-A46739B44B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9332AB87-30CD-4DDA-8D9B-0A5497A1DD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23250" yWindow="1980" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -63,7 +63,7 @@
     <t>135361779</t>
   </si>
   <si>
-    <t xml:space="preserve">RECUSAS MDS 17.11.2025 </t>
+    <t>RECUSAS MDS 17.11.2025</t>
   </si>
 </sst>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9332AB87-30CD-4DDA-8D9B-0A5497A1DD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240C0D65-7D69-4A19-A35B-5312510BA9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23250" yWindow="1980" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -61,16 +61,13 @@
   </si>
   <si>
     <t>135361779</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 17.11.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,6 +85,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -140,6 +145,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -500,7 +508,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -517,8 +525,8 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -538,31 +546,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240C0D65-7D69-4A19-A35B-5312510BA9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A399B8E-D638-451D-A584-816E43CAD360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23250" yWindow="1980" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>135346571</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 17.11.2025</t>
-  </si>
-  <si>
-    <t>135361779</t>
+    <t>135381729</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 18.11.2025</t>
+  </si>
+  <si>
+    <t>135440699</t>
+  </si>
+  <si>
+    <t>Relatório de RECUSA MDS 18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -508,7 +511,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -526,7 +529,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -546,31 +549,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A399B8E-D638-451D-A584-816E43CAD360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7AED8A-CC6E-455D-A02B-F0A172B666C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -549,31 +549,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7AED8A-CC6E-455D-A02B-F0A172B666C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FB95C4-5CF7-4A08-BB62-60D513CBD1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -63,7 +63,7 @@
     <t>135440699</t>
   </si>
   <si>
-    <t>Relatório de RECUSA MDS 18.11.2025</t>
+    <t>RECUSA MDS 18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -549,31 +549,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FB95C4-5CF7-4A08-BB62-60D513CBD1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EBE74D-FA6D-47A8-8B9D-DE982B91474F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,23 +54,38 @@
     <t>971</t>
   </si>
   <si>
-    <t>135381729</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 18.11.2025</t>
-  </si>
-  <si>
-    <t>135440699</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 18.11.2025</t>
+    <t>135368522</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 19.11.2025</t>
+  </si>
+  <si>
+    <t>135422250</t>
+  </si>
+  <si>
+    <t>135451207</t>
+  </si>
+  <si>
+    <t>135454863</t>
+  </si>
+  <si>
+    <t>135449393</t>
+  </si>
+  <si>
+    <t>135342538</t>
+  </si>
+  <si>
+    <t>135362660</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 19.11.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,14 +103,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -133,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -148,9 +155,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -470,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -511,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -528,10 +532,95 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EBE74D-FA6D-47A8-8B9D-DE982B91474F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B39F8C2-B991-4EB2-AD9B-C4DFA5754820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,31 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>135368522</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 19.11.2025</t>
-  </si>
-  <si>
-    <t>135422250</t>
-  </si>
-  <si>
-    <t>135451207</t>
-  </si>
-  <si>
-    <t>135454863</t>
-  </si>
-  <si>
-    <t>135449393</t>
-  </si>
-  <si>
-    <t>135342538</t>
-  </si>
-  <si>
-    <t>135362660</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 19.11.2025</t>
+    <t>135423785</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 21.11.2025</t>
+  </si>
+  <si>
+    <t>135442479</t>
+  </si>
+  <si>
+    <t>135386611</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 21.11.2025</t>
   </si>
 </sst>
 </file>
@@ -474,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -515,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -533,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -550,77 +538,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -638,31 +558,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B39F8C2-B991-4EB2-AD9B-C4DFA5754820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053E0171-E2E9-4EF7-8972-1B001B34481E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>135423785</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 21.11.2025</t>
-  </si>
-  <si>
-    <t>135442479</t>
-  </si>
-  <si>
-    <t>135386611</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 21.11.2025</t>
+    <t>135400970</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 24.11.2025</t>
+  </si>
+  <si>
+    <t>135470957</t>
+  </si>
+  <si>
+    <t>135498739</t>
+  </si>
+  <si>
+    <t>135488360</t>
+  </si>
+  <si>
+    <t>135427432</t>
+  </si>
+  <si>
+    <t>135398595</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 24.11.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -538,9 +547,60 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -558,31 +618,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053E0171-E2E9-4EF7-8972-1B001B34481E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B21AB8-5DA4-426E-B805-59D4477B6F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>135400970</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 24.11.2025</t>
-  </si>
-  <si>
-    <t>135470957</t>
-  </si>
-  <si>
-    <t>135498739</t>
-  </si>
-  <si>
-    <t>135488360</t>
-  </si>
-  <si>
-    <t>135427432</t>
-  </si>
-  <si>
-    <t>135398595</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 24.11.2025</t>
+    <t>135514136</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 25.11.2025</t>
+  </si>
+  <si>
+    <t>135518626</t>
+  </si>
+  <si>
+    <t>135547735</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 25.11.2025</t>
   </si>
 </sst>
 </file>
@@ -471,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -512,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -530,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -547,60 +538,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -618,31 +558,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B21AB8-5DA4-426E-B805-59D4477B6F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16004363-537E-429C-8977-AAF97E23FFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>135514136</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 25.11.2025</t>
-  </si>
-  <si>
-    <t>135518626</t>
-  </si>
-  <si>
-    <t>135547735</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 25.11.2025</t>
+    <t>135506476</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 26.11.2025</t>
+  </si>
+  <si>
+    <t>130814101</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 26.11.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,26 +518,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -558,31 +538,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348DF617-434B-4D2C-AE8E-4D0686A9EF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6817607F-751E-48C1-8387-79F0D90D1A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,13 +54,13 @@
     <t>971</t>
   </si>
   <si>
-    <t>135512506</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 27.11.2025</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 27.11.2025</t>
+    <t>135620708</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 29.11.2025</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 29.11.2025</t>
   </si>
 </sst>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6817607F-751E-48C1-8387-79F0D90D1A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BCC79B-4220-4EB5-BC3C-28FBB4CE4993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>135620708</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 29.11.2025</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 29.11.2025</t>
+    <t>135616309</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 01.12.2025</t>
+  </si>
+  <si>
+    <t>135607094</t>
+  </si>
+  <si>
+    <t>135617803</t>
+  </si>
+  <si>
+    <t>135441318</t>
+  </si>
+  <si>
+    <t>135522552</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 01.12.2025</t>
   </si>
 </sst>
 </file>
@@ -456,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,12 +509,80 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -518,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BCC79B-4220-4EB5-BC3C-28FBB4CE4993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68C093E-E373-49F3-B8E8-F62834B99A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>135616309</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 01.12.2025</t>
-  </si>
-  <si>
-    <t>135607094</t>
-  </si>
-  <si>
-    <t>135617803</t>
-  </si>
-  <si>
-    <t>135441318</t>
-  </si>
-  <si>
-    <t>135522552</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 01.12.2025</t>
+    <t>135466343</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 02.12.2025</t>
+  </si>
+  <si>
+    <t>135573520</t>
+  </si>
+  <si>
+    <t>135658522</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 02.12.2025</t>
   </si>
 </sst>
 </file>
@@ -468,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -527,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -544,43 +538,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -598,31 +558,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68C093E-E373-49F3-B8E8-F62834B99A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CFE1D2-D9D9-422A-A70B-AA92AAF12634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,13 @@
     <t>971</t>
   </si>
   <si>
-    <t>135466343</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 02.12.2025</t>
-  </si>
-  <si>
-    <t>135573520</t>
-  </si>
-  <si>
-    <t>135658522</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 02.12.2025</t>
+    <t>135674077</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 03.12.2025</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 03.12.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +456,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,46 +497,12 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -558,31 +518,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CFE1D2-D9D9-422A-A70B-AA92AAF12634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B28A3B-57A8-4714-A9DB-2CFDE63DDA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="885" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,13 +54,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>135674077</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 03.12.2025</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 03.12.2025</t>
+    <t>135679000</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 04.12.2025</t>
+  </si>
+  <si>
+    <t>135678630</t>
+  </si>
+  <si>
+    <t>135518413</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 04.12.2025</t>
   </si>
 </sst>
 </file>
@@ -456,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,12 +503,46 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -518,31 +558,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B28A3B-57A8-4714-A9DB-2CFDE63DDA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681400D8-36E6-46C9-9547-EA8F47461CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="885" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,19 +54,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>135679000</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 04.12.2025</t>
-  </si>
-  <si>
-    <t>135678630</t>
-  </si>
-  <si>
-    <t>135518413</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 04.12.2025</t>
+    <t>135505518</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 05.12.2025</t>
+  </si>
+  <si>
+    <t>135618411</t>
+  </si>
+  <si>
+    <t>135513980</t>
+  </si>
+  <si>
+    <t>135522969</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 05.12.2025</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -538,9 +541,26 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -558,31 +578,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681400D8-36E6-46C9-9547-EA8F47461CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7BD5A4-785E-4CCB-9FDA-AE76F8D919FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1230" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>135505518</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 05.12.2025</t>
-  </si>
-  <si>
-    <t>135618411</t>
-  </si>
-  <si>
-    <t>135513980</t>
-  </si>
-  <si>
-    <t>135522969</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 05.12.2025</t>
+    <t>135532176</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 08.12.2025</t>
+  </si>
+  <si>
+    <t>135661490</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 08.12.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -524,43 +518,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -578,31 +538,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1BA114-D83E-41C4-854F-42BD87003A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918BF115-EA72-4057-9733-60DE6B921AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,22 +54,37 @@
     <t>971</t>
   </si>
   <si>
-    <t>135068836</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 28.10.2025</t>
-  </si>
-  <si>
-    <t>134982699</t>
-  </si>
-  <si>
-    <t>135140926</t>
-  </si>
-  <si>
-    <t>135090961</t>
-  </si>
-  <si>
-    <t>RECUSAS MDS 28.10.2025</t>
+    <t>135864562</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 19.12.2025</t>
+  </si>
+  <si>
+    <t>135936438</t>
+  </si>
+  <si>
+    <t>132666165</t>
+  </si>
+  <si>
+    <t>135945939</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 20.12.2025</t>
+  </si>
+  <si>
+    <t>135967541</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 21.12.2025</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 19.12.2025</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 20.12.2025</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 21.12.2025</t>
   </si>
 </sst>
 </file>
@@ -465,7 +480,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -524,7 +539,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -541,7 +556,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -555,12 +570,29 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -578,31 +610,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918BF115-EA72-4057-9733-60DE6B921AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455D886D-BF9F-43A9-890C-A7D3B0E5AC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,37 +54,34 @@
     <t>971</t>
   </si>
   <si>
-    <t>135864562</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 19.12.2025</t>
-  </si>
-  <si>
-    <t>135936438</t>
-  </si>
-  <si>
-    <t>132666165</t>
-  </si>
-  <si>
-    <t>135945939</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 20.12.2025</t>
-  </si>
-  <si>
-    <t>135967541</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 21.12.2025</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 19.12.2025</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 20.12.2025</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 21.12.2025</t>
+    <t>135758047</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 22.12.2025</t>
+  </si>
+  <si>
+    <t>135775137</t>
+  </si>
+  <si>
+    <t>135880946</t>
+  </si>
+  <si>
+    <t>135742263</t>
+  </si>
+  <si>
+    <t>135978006</t>
+  </si>
+  <si>
+    <t>135986358</t>
+  </si>
+  <si>
+    <t>135905610</t>
+  </si>
+  <si>
+    <t>135796735</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 22.12.2025</t>
   </si>
 </sst>
 </file>
@@ -480,7 +477,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -521,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -539,7 +536,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -556,7 +553,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -570,7 +567,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
@@ -581,18 +578,69 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -610,31 +658,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455D886D-BF9F-43A9-890C-A7D3B0E5AC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CFAB09-2214-498F-BDDE-F34B4DA42E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,25 @@
     <t>971</t>
   </si>
   <si>
-    <t>135758047</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 22.12.2025</t>
-  </si>
-  <si>
-    <t>135775137</t>
-  </si>
-  <si>
-    <t>135880946</t>
-  </si>
-  <si>
-    <t>135742263</t>
-  </si>
-  <si>
-    <t>135978006</t>
-  </si>
-  <si>
-    <t>135986358</t>
-  </si>
-  <si>
-    <t>135905610</t>
-  </si>
-  <si>
-    <t>135796735</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 22.12.2025</t>
+    <t>135819154</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 23.12.2025</t>
+  </si>
+  <si>
+    <t>135924514</t>
+  </si>
+  <si>
+    <t>135989608</t>
+  </si>
+  <si>
+    <t>135800480</t>
+  </si>
+  <si>
+    <t>888213819</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 23.12.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -518,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -536,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -553,7 +544,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -570,7 +561,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -587,60 +578,9 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -658,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CFAB09-2214-498F-BDDE-F34B4DA42E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF3423D-983B-4059-9690-1295D9B9EE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,25 +54,40 @@
     <t>971</t>
   </si>
   <si>
-    <t>135819154</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 23.12.2025</t>
-  </si>
-  <si>
-    <t>135924514</t>
-  </si>
-  <si>
-    <t>135989608</t>
-  </si>
-  <si>
-    <t>135800480</t>
-  </si>
-  <si>
-    <t>888213819</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 23.12.2025</t>
+    <t>135869140</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 26.12.2025</t>
+  </si>
+  <si>
+    <t>135923254</t>
+  </si>
+  <si>
+    <t>135934982</t>
+  </si>
+  <si>
+    <t>135871639</t>
+  </si>
+  <si>
+    <t>135489939</t>
+  </si>
+  <si>
+    <t>135877627</t>
+  </si>
+  <si>
+    <t>136029220</t>
+  </si>
+  <si>
+    <t>135887739</t>
+  </si>
+  <si>
+    <t>135889628</t>
+  </si>
+  <si>
+    <t>135834645</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 26.12.2025</t>
   </si>
 </sst>
 </file>
@@ -468,7 +483,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -527,7 +542,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -544,7 +559,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -561,7 +576,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -578,9 +593,94 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -598,31 +698,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF3423D-983B-4059-9690-1295D9B9EE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB93BF7-5F40-40C4-955F-D0AAC4ADDCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,40 +54,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>135869140</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 26.12.2025</t>
-  </si>
-  <si>
-    <t>135923254</t>
-  </si>
-  <si>
-    <t>135934982</t>
-  </si>
-  <si>
-    <t>135871639</t>
-  </si>
-  <si>
-    <t>135489939</t>
-  </si>
-  <si>
-    <t>135877627</t>
-  </si>
-  <si>
-    <t>136029220</t>
-  </si>
-  <si>
-    <t>135887739</t>
-  </si>
-  <si>
-    <t>135889628</t>
-  </si>
-  <si>
-    <t>135834645</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 26.12.2025</t>
+    <t>135891227</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 29.12.2025</t>
+  </si>
+  <si>
+    <t>135901605</t>
+  </si>
+  <si>
+    <t>136041929</t>
+  </si>
+  <si>
+    <t>134210961</t>
+  </si>
+  <si>
+    <t>135935829</t>
+  </si>
+  <si>
+    <t>135960249</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 29.12.2025</t>
   </si>
 </sst>
 </file>
@@ -483,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -524,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -542,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -559,7 +547,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -576,7 +564,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -593,7 +581,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -610,77 +598,9 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -698,31 +618,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB93BF7-5F40-40C4-955F-D0AAC4ADDCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5B5C30-4E78-457C-8439-85B8C7A49596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,54 +28,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
   <si>
-    <t>Nº recibo</t>
-  </si>
-  <si>
-    <t>sem juros/com juros</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mensagem </t>
   </si>
   <si>
-    <t xml:space="preserve">Modelo/Descrição </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anexo </t>
-  </si>
-  <si>
     <t>Processar</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>135891227</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 29.12.2025</t>
-  </si>
-  <si>
-    <t>135901605</t>
-  </si>
-  <si>
-    <t>136041929</t>
-  </si>
-  <si>
-    <t>134210961</t>
-  </si>
-  <si>
-    <t>135935829</t>
-  </si>
-  <si>
-    <t>135960249</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 29.12.2025</t>
+    <t>135910834</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 30.12.25</t>
+  </si>
+  <si>
+    <t>136048789</t>
+  </si>
+  <si>
+    <t>136043245</t>
+  </si>
+  <si>
+    <t>135908348</t>
+  </si>
+  <si>
+    <t>135902091</t>
+  </si>
+  <si>
+    <t>135133476</t>
+  </si>
+  <si>
+    <t>136073091</t>
   </si>
 </sst>
 </file>
@@ -471,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -482,126 +470,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
       <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -618,31 +615,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5B5C30-4E78-457C-8439-85B8C7A49596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2A2894-871C-43DF-8817-6B6282C00454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -42,28 +42,13 @@
     <t>971</t>
   </si>
   <si>
-    <t>135910834</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 30.12.25</t>
-  </si>
-  <si>
-    <t>136048789</t>
-  </si>
-  <si>
-    <t>136043245</t>
-  </si>
-  <si>
-    <t>135908348</t>
-  </si>
-  <si>
-    <t>135902091</t>
-  </si>
-  <si>
-    <t>135133476</t>
-  </si>
-  <si>
-    <t>136073091</t>
+    <t>136098436</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 05.01.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 05.01.2026</t>
   </si>
 </sst>
 </file>
@@ -459,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -492,114 +477,12 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -615,31 +498,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2A2894-871C-43DF-8817-6B6282C00454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E318AF9-8D86-434B-87D4-946747E2A938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -42,13 +42,19 @@
     <t>971</t>
   </si>
   <si>
-    <t>136098436</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 05.01.2026</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 05.01.2026</t>
+    <t>136059366</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 07.01.2026</t>
+  </si>
+  <si>
+    <t>135997599</t>
+  </si>
+  <si>
+    <t>136060573</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 07.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +450,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -477,12 +483,46 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -498,31 +538,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E318AF9-8D86-434B-87D4-946747E2A938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFED71A3-C295-4838-9F3A-594CC061DF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -42,19 +42,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>136059366</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 07.01.2026</t>
-  </si>
-  <si>
-    <t>135997599</t>
-  </si>
-  <si>
-    <t>136060573</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 07.01.2026</t>
+    <t>136029922</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 08.01.2026</t>
+  </si>
+  <si>
+    <t>136025401</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 08.01.2026</t>
   </si>
 </sst>
 </file>
@@ -450,7 +447,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -483,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -501,26 +498,9 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -538,31 +518,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFED71A3-C295-4838-9F3A-594CC061DF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC8E828-8342-491B-9775-226AFBD3047E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -42,16 +42,31 @@
     <t>971</t>
   </si>
   <si>
-    <t>136029922</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 08.01.2026</t>
-  </si>
-  <si>
-    <t>136025401</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 08.01.2026</t>
+    <t>136050753</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 10.01.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 10.01.2026</t>
+  </si>
+  <si>
+    <t>136084087</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 09.01.2026</t>
+  </si>
+  <si>
+    <t>136060578</t>
+  </si>
+  <si>
+    <t>136063179</t>
+  </si>
+  <si>
+    <t>136064260</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 09.01.2026</t>
   </si>
 </sst>
 </file>
@@ -447,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -480,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -489,18 +504,69 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC8E828-8342-491B-9775-226AFBD3047E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C129F8-1DA7-4484-B1B3-9AD31A6E4E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -42,31 +42,16 @@
     <t>971</t>
   </si>
   <si>
-    <t>136050753</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 10.01.2026</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 10.01.2026</t>
-  </si>
-  <si>
-    <t>136084087</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 09.01.2026</t>
-  </si>
-  <si>
-    <t>136060578</t>
-  </si>
-  <si>
-    <t>136063179</t>
-  </si>
-  <si>
-    <t>136064260</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 09.01.2026</t>
+    <t>136189274</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 12.01.2026</t>
+  </si>
+  <si>
+    <t>132579138</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 12.01.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +447,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -495,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -504,69 +489,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -584,31 +518,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C129F8-1DA7-4484-B1B3-9AD31A6E4E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37C51DD-0392-4AEA-8232-7D57919EE381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -42,16 +42,28 @@
     <t>971</t>
   </si>
   <si>
-    <t>136189274</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 12.01.2026</t>
-  </si>
-  <si>
-    <t>132579138</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 12.01.2026</t>
+    <t>136083803</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 13.01.2026</t>
+  </si>
+  <si>
+    <t>136105548</t>
+  </si>
+  <si>
+    <t>136105828</t>
+  </si>
+  <si>
+    <t>136197368</t>
+  </si>
+  <si>
+    <t>136072194</t>
+  </si>
+  <si>
+    <t>136103814</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 13.01.2026</t>
   </si>
 </sst>
 </file>
@@ -447,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -480,7 +492,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -498,9 +510,77 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -518,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37C51DD-0392-4AEA-8232-7D57919EE381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713DD5B9-5432-4E8F-9946-A243BEE2358D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -42,28 +42,22 @@
     <t>971</t>
   </si>
   <si>
-    <t>136083803</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 13.01.2026</t>
-  </si>
-  <si>
-    <t>136105548</t>
-  </si>
-  <si>
-    <t>136105828</t>
-  </si>
-  <si>
-    <t>136197368</t>
-  </si>
-  <si>
-    <t>136072194</t>
-  </si>
-  <si>
-    <t>136103814</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 13.01.2026</t>
+    <t>136090026</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 14.01.2026</t>
+  </si>
+  <si>
+    <t>136212337</t>
+  </si>
+  <si>
+    <t>136217662</t>
+  </si>
+  <si>
+    <t>136106364</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -459,7 +453,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -492,7 +486,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>2</v>
@@ -510,7 +504,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
@@ -527,7 +521,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>2</v>
@@ -544,43 +538,9 @@
         <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -598,31 +558,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713DD5B9-5432-4E8F-9946-A243BEE2358D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19526D80-9A7E-4ACD-8EC2-D9A459F72034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,36 +28,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
   <si>
+    <t>Nº recibo</t>
+  </si>
+  <si>
+    <t>sem juros/com juros</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mensagem </t>
   </si>
   <si>
+    <t xml:space="preserve">Modelo/Descrição </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anexo </t>
+  </si>
+  <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>136090026</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 14.01.2026</t>
-  </si>
-  <si>
-    <t>136212337</t>
-  </si>
-  <si>
-    <t>136217662</t>
-  </si>
-  <si>
-    <t>136106364</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -464,84 +455,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19526D80-9A7E-4ACD-8EC2-D9A459F72034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,18 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136098732</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 15.01.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 15.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +456,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,30 +487,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -514,31 +518,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63FCF5F-B2B6-4DD9-9763-CEC2F8F300DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,16 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136098732</t>
+    <t>136286474</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 15.01.2026</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 15.01.2026</t>
+    <t>Relatório de Recusa MDS 16.01.2026</t>
+  </si>
+  <si>
+    <t>136118901</t>
+  </si>
+  <si>
+    <t>136177249</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 16.01.2026</t>
   </si>
 </sst>
 </file>
@@ -456,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,12 +503,46 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63FCF5F-B2B6-4DD9-9763-CEC2F8F300DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C685E4-0558-4259-A23B-7CBC906E4240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,22 +51,28 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136286474</t>
+    <t>136122036</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 16.01.2026</t>
-  </si>
-  <si>
-    <t>136118901</t>
-  </si>
-  <si>
-    <t>136177249</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 16.01.2026</t>
+    <t>Relatório de Recusa MDS 19.01.2026</t>
+  </si>
+  <si>
+    <t>136227130</t>
+  </si>
+  <si>
+    <t>136270382</t>
+  </si>
+  <si>
+    <t>136283669</t>
+  </si>
+  <si>
+    <t>136140582</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 19.01.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +509,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -538,9 +544,43 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C685E4-0558-4259-A23B-7CBC906E4240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0B5993-65AE-47C1-BE21-AD26F01BF664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,28 +51,19 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136122036</t>
+    <t>136323883</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 19.01.2026</t>
-  </si>
-  <si>
-    <t>136227130</t>
-  </si>
-  <si>
-    <t>136270382</t>
-  </si>
-  <si>
-    <t>136283669</t>
-  </si>
-  <si>
-    <t>136140582</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 19.01.2026</t>
+    <t>Relatório de Recusa MDS 20.01.2026</t>
+  </si>
+  <si>
+    <t>136138574</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 20.01.2026</t>
   </si>
 </sst>
 </file>
@@ -468,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -509,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -527,60 +518,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0B5993-65AE-47C1-BE21-AD26F01BF664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2D3D6E-65BF-4535-9426-95C6838E94F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,19 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136323883</t>
+    <t>136163471</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 20.01.2026</t>
-  </si>
-  <si>
-    <t>136138574</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 20.01.2026</t>
+    <t>Relatório de Recusa MDS 21.01.2026</t>
+  </si>
+  <si>
+    <t>136188645</t>
+  </si>
+  <si>
+    <t>136156887</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 21.01.2026</t>
   </si>
 </sst>
 </file>
@@ -459,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -518,9 +521,26 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2D3D6E-65BF-4535-9426-95C6838E94F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867ED5B6-7912-481C-AAA0-2D5402308B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,22 +51,25 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136163471</t>
+    <t>136153898</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 21.01.2026</t>
-  </si>
-  <si>
-    <t>136188645</t>
-  </si>
-  <si>
-    <t>136156887</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 21.01.2026</t>
+    <t>Relatório de Recusa MDS 22.01.2026</t>
+  </si>
+  <si>
+    <t>136280685</t>
+  </si>
+  <si>
+    <t>136169838</t>
+  </si>
+  <si>
+    <t>132634182</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 22.01.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -538,9 +541,26 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867ED5B6-7912-481C-AAA0-2D5402308B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B728C7-EC03-4B6D-9DA8-09FF83F0577A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,25 +51,46 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136153898</t>
+    <t>136261991</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 22.01.2026</t>
-  </si>
-  <si>
-    <t>136280685</t>
-  </si>
-  <si>
-    <t>136169838</t>
-  </si>
-  <si>
-    <t>132634182</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 22.01.2026</t>
+    <t>Relatório de Recusa MDS 23.01.2026</t>
+  </si>
+  <si>
+    <t>136269259</t>
+  </si>
+  <si>
+    <t>136200515</t>
+  </si>
+  <si>
+    <t>131413373</t>
+  </si>
+  <si>
+    <t>136221942</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 23.01.2026</t>
+  </si>
+  <si>
+    <t>136199627</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 24.01.2026</t>
+  </si>
+  <si>
+    <t>136239579</t>
+  </si>
+  <si>
+    <t>136243400</t>
+  </si>
+  <si>
+    <t>136245249</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 24.01.2026</t>
   </si>
 </sst>
 </file>
@@ -465,7 +486,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -524,7 +545,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -541,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -558,9 +579,94 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -578,31 +684,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B728C7-EC03-4B6D-9DA8-09FF83F0577A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,48 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136261991</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 23.01.2026</t>
-  </si>
-  <si>
-    <t>136269259</t>
-  </si>
-  <si>
-    <t>136200515</t>
-  </si>
-  <si>
-    <t>131413373</t>
-  </si>
-  <si>
-    <t>136221942</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 23.01.2026</t>
-  </si>
-  <si>
-    <t>136199627</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 24.01.2026</t>
-  </si>
-  <si>
-    <t>136239579</t>
-  </si>
-  <si>
-    <t>136243400</t>
-  </si>
-  <si>
-    <t>136245249</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 24.01.2026</t>
   </si>
 </sst>
 </file>
@@ -486,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -517,156 +475,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D5E25D-CE5C-4478-AE7D-C6FD45F13031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,33 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136385382</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 26.01.2026</t>
+  </si>
+  <si>
+    <t>136208552</t>
+  </si>
+  <si>
+    <t>136213890</t>
+  </si>
+  <si>
+    <t>136228937</t>
+  </si>
+  <si>
+    <t>136269659</t>
+  </si>
+  <si>
+    <t>136414526</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -475,32 +502,104 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
@@ -519,31 +618,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D5E25D-CE5C-4478-AE7D-C6FD45F13031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,33 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136385382</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 26.01.2026</t>
-  </si>
-  <si>
-    <t>136208552</t>
-  </si>
-  <si>
-    <t>136213890</t>
-  </si>
-  <si>
-    <t>136228937</t>
-  </si>
-  <si>
-    <t>136269659</t>
-  </si>
-  <si>
-    <t>136414526</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -502,104 +475,32 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
@@ -618,31 +519,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E6923B-D6B0-4335-B702-56F5C157D802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,18 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136326395</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 27.01.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 27.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +456,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,35 +487,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -519,31 +518,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E6923B-D6B0-4335-B702-56F5C157D802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51788AC6-1E06-473B-92D1-40A37FEA2A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,16 +51,34 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136326395</t>
+    <t>136380446</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 27.01.2026</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 27.01.2026</t>
+    <t>Relatório de Recusa MDS 28.01.2026</t>
+  </si>
+  <si>
+    <t>136220105</t>
+  </si>
+  <si>
+    <t>136291312</t>
+  </si>
+  <si>
+    <t>136318975</t>
+  </si>
+  <si>
+    <t>136255140</t>
+  </si>
+  <si>
+    <t>136266015</t>
+  </si>
+  <si>
+    <t>136451697</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -456,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -497,12 +515,114 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51788AC6-1E06-473B-92D1-40A37FEA2A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,36 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136380446</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 28.01.2026</t>
-  </si>
-  <si>
-    <t>136220105</t>
-  </si>
-  <si>
-    <t>136291312</t>
-  </si>
-  <si>
-    <t>136318975</t>
-  </si>
-  <si>
-    <t>136255140</t>
-  </si>
-  <si>
-    <t>136266015</t>
-  </si>
-  <si>
-    <t>136451697</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -474,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -505,122 +475,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -638,31 +519,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9D8E08-A3E2-4CA9-8CEA-6017258AE46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23355" yWindow="2085" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136291723</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 29.01.2026</t>
+  </si>
+  <si>
+    <t>136392439</t>
+  </si>
+  <si>
+    <t>136386948</t>
+  </si>
+  <si>
+    <t>136275778</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 29.01.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,33 +496,71 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,31 +578,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9D8E08-A3E2-4CA9-8CEA-6017258AE46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
-    <workbookView xWindow="23355" yWindow="2085" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,27 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136291723</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 29.01.2026</t>
-  </si>
-  <si>
-    <t>136392439</t>
-  </si>
-  <si>
-    <t>136386948</t>
-  </si>
-  <si>
-    <t>136275778</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 29.01.2026</t>
   </si>
 </sst>
 </file>
@@ -465,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -496,71 +475,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -578,31 +519,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09009557-6E69-4E4C-87C5-34CD7986ECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,36 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136405431</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 02.02.2026</t>
+  </si>
+  <si>
+    <t>136421919</t>
+  </si>
+  <si>
+    <t>136445463</t>
+  </si>
+  <si>
+    <t>136468636</t>
+  </si>
+  <si>
+    <t>136328362</t>
+  </si>
+  <si>
+    <t>136329071</t>
+  </si>
+  <si>
+    <t>136413031</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 02.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,33 +505,122 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,31 +638,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09009557-6E69-4E4C-87C5-34CD7986ECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AC7D26-ECCD-4C88-B13D-B3B6B54F210A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,34 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136405431</t>
+    <t>136379552</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 02.02.2026</t>
-  </si>
-  <si>
-    <t>136421919</t>
-  </si>
-  <si>
-    <t>136445463</t>
-  </si>
-  <si>
-    <t>136468636</t>
-  </si>
-  <si>
-    <t>136328362</t>
-  </si>
-  <si>
-    <t>136329071</t>
-  </si>
-  <si>
-    <t>136413031</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 02.02.2026</t>
+    <t>Relatório de Recusa MDS 03.02.2026</t>
+  </si>
+  <si>
+    <t>136491256</t>
+  </si>
+  <si>
+    <t>136351308</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 03.02.2026</t>
   </si>
 </sst>
 </file>
@@ -474,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -515,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -533,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -550,77 +538,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AC7D26-ECCD-4C88-B13D-B3B6B54F210A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7369F98C-CDDF-4363-9FBF-91517115AE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,22 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136379552</t>
+    <t>136364738</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 03.02.2026</t>
-  </si>
-  <si>
-    <t>136491256</t>
-  </si>
-  <si>
-    <t>136351308</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 03.02.2026</t>
+    <t>Relatório de Recusa MDS 04.02.2026</t>
+  </si>
+  <si>
+    <t>136466884</t>
+  </si>
+  <si>
+    <t>136467103</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 04.02.2026</t>
   </si>
 </sst>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7369F98C-CDDF-4363-9FBF-91517115AE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,24 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136364738</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 04.02.2026</t>
-  </si>
-  <si>
-    <t>136466884</t>
-  </si>
-  <si>
-    <t>136467103</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 04.02.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -493,54 +475,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -558,31 +519,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945F7841-49B2-4357-9F14-E2E86E600065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,33 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136485049</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 05.02.2026</t>
+  </si>
+  <si>
+    <t>136493483</t>
+  </si>
+  <si>
+    <t>136554753</t>
+  </si>
+  <si>
+    <t>136368335</t>
+  </si>
+  <si>
+    <t>135609255</t>
+  </si>
+  <si>
+    <t>136383434</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 05.02.2026</t>
   </si>
 </sst>
 </file>
@@ -475,32 +502,104 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
@@ -519,31 +618,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945F7841-49B2-4357-9F14-E2E86E600065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F5B9B-3909-4C3A-AF10-9E10F7AAA85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,22 +51,16 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136485049</t>
+    <t>136577260</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 05.02.2026</t>
-  </si>
-  <si>
-    <t>136493483</t>
-  </si>
-  <si>
-    <t>136554753</t>
-  </si>
-  <si>
-    <t>136368335</t>
+    <t>Relatório de Recusa MDS 06.02.2026</t>
+  </si>
+  <si>
+    <t>136578652</t>
   </si>
   <si>
     <t>135609255</t>
@@ -75,7 +69,28 @@
     <t>136383434</t>
   </si>
   <si>
-    <t>RECUSA MDS 05.02.2026</t>
+    <t>136430411</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 06.02.2026</t>
+  </si>
+  <si>
+    <t>136447668</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 09.02.2026</t>
+  </si>
+  <si>
+    <t>136447674</t>
+  </si>
+  <si>
+    <t>136445272</t>
+  </si>
+  <si>
+    <t>136448004</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 09.02.2026</t>
   </si>
 </sst>
 </file>
@@ -471,7 +486,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -512,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -530,7 +545,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -547,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -564,7 +579,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -572,7 +587,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
@@ -581,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -589,7 +604,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
@@ -598,9 +613,94 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F5B9B-3909-4C3A-AF10-9E10F7AAA85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,48 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136577260</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 06.02.2026</t>
-  </si>
-  <si>
-    <t>136578652</t>
-  </si>
-  <si>
-    <t>135609255</t>
-  </si>
-  <si>
-    <t>136383434</t>
-  </si>
-  <si>
-    <t>136430411</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 06.02.2026</t>
-  </si>
-  <si>
-    <t>136447668</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 09.02.2026</t>
-  </si>
-  <si>
-    <t>136447674</t>
-  </si>
-  <si>
-    <t>136445272</t>
-  </si>
-  <si>
-    <t>136448004</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 09.02.2026</t>
   </si>
 </sst>
 </file>
@@ -486,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -517,190 +475,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -718,31 +519,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0085CFCC-7F6D-4C21-88A4-493DCFFBFCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,57 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136447668</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 09.02.2026</t>
+  </si>
+  <si>
+    <t>136447674</t>
+  </si>
+  <si>
+    <t>136445272</t>
+  </si>
+  <si>
+    <t>136448004</t>
+  </si>
+  <si>
+    <t>136554315</t>
+  </si>
+  <si>
+    <t>136556183</t>
+  </si>
+  <si>
+    <t>136419345</t>
+  </si>
+  <si>
+    <t>136640714</t>
+  </si>
+  <si>
+    <t>136447876</t>
+  </si>
+  <si>
+    <t>136385104</t>
+  </si>
+  <si>
+    <t>136642498</t>
+  </si>
+  <si>
+    <t>136644513</t>
+  </si>
+  <si>
+    <t>136466366</t>
+  </si>
+  <si>
+    <t>136488074</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 09.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +495,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,33 +526,241 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,31 +778,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0085CFCC-7F6D-4C21-88A4-493DCFFBFCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155CFCD9-96E1-40E3-8E5D-4C709AD3B753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,55 +51,22 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136447668</t>
+    <t>136517750</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 09.02.2026</t>
-  </si>
-  <si>
-    <t>136447674</t>
-  </si>
-  <si>
-    <t>136445272</t>
-  </si>
-  <si>
-    <t>136448004</t>
-  </si>
-  <si>
-    <t>136554315</t>
-  </si>
-  <si>
-    <t>136556183</t>
-  </si>
-  <si>
-    <t>136419345</t>
-  </si>
-  <si>
-    <t>136640714</t>
-  </si>
-  <si>
-    <t>136447876</t>
-  </si>
-  <si>
-    <t>136385104</t>
-  </si>
-  <si>
-    <t>136642498</t>
-  </si>
-  <si>
-    <t>136644513</t>
-  </si>
-  <si>
-    <t>136466366</t>
-  </si>
-  <si>
-    <t>136488074</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 09.02.2026</t>
+    <t>Relatório de Recusa MDS 10.02.2026</t>
+  </si>
+  <si>
+    <t>136671529</t>
+  </si>
+  <si>
+    <t>136554542</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 10..02.2026</t>
   </si>
 </sst>
 </file>
@@ -495,7 +462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -536,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -554,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -571,196 +538,9 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155CFCD9-96E1-40E3-8E5D-4C709AD3B753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063D46B3-69D9-459A-AD02-13B0D012D402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,22 +51,19 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136517750</t>
+    <t>134404456</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 10.02.2026</t>
-  </si>
-  <si>
-    <t>136671529</t>
-  </si>
-  <si>
-    <t>136554542</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 10..02.2026</t>
+    <t>Relatório de Recusa MDS 11.02.2026</t>
+  </si>
+  <si>
+    <t>136450691</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 11.02.2026</t>
   </si>
 </sst>
 </file>
@@ -462,7 +459,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -503,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -521,26 +518,9 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063D46B3-69D9-459A-AD02-13B0D012D402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245BA8B3-594A-4F41-B3D9-40D2A74A1FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,19 +51,19 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>134404456</t>
+    <t>136564142</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 11.02.2026</t>
-  </si>
-  <si>
-    <t>136450691</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 11.02.2026</t>
+    <t>Relatório de Recusa MDS 12.02.2026</t>
+  </si>
+  <si>
+    <t>136578629</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 12.02.2026</t>
   </si>
 </sst>
 </file>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF538C3-122B-433C-BC90-15D769BE2864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,72 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136548869</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 18.02.2026</t>
+  </si>
+  <si>
+    <t>136701698</t>
+  </si>
+  <si>
+    <t>136548369</t>
+  </si>
+  <si>
+    <t>136594001</t>
+  </si>
+  <si>
+    <t>136606501</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 18.02.2026</t>
+  </si>
+  <si>
+    <t>136552651</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 16.02.2026</t>
+  </si>
+  <si>
+    <t>136695224</t>
+  </si>
+  <si>
+    <t>136500968</t>
+  </si>
+  <si>
+    <t>136502095</t>
+  </si>
+  <si>
+    <t>136527894</t>
+  </si>
+  <si>
+    <t>136526655</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 16.02.2026</t>
+  </si>
+  <si>
+    <t>136526201</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 15.02.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 15.02.2026</t>
+  </si>
+  <si>
+    <t>136715558</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 13.02.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 13.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +510,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,33 +541,224 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,31 +776,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF538C3-122B-433C-BC90-15D769BE2864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,72 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136548869</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 18.02.2026</t>
-  </si>
-  <si>
-    <t>136701698</t>
-  </si>
-  <si>
-    <t>136548369</t>
-  </si>
-  <si>
-    <t>136594001</t>
-  </si>
-  <si>
-    <t>136606501</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 18.02.2026</t>
-  </si>
-  <si>
-    <t>136552651</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 16.02.2026</t>
-  </si>
-  <si>
-    <t>136695224</t>
-  </si>
-  <si>
-    <t>136500968</t>
-  </si>
-  <si>
-    <t>136502095</t>
-  </si>
-  <si>
-    <t>136527894</t>
-  </si>
-  <si>
-    <t>136526655</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 16.02.2026</t>
-  </si>
-  <si>
-    <t>136526201</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 15.02.2026</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 15.02.2026</t>
-  </si>
-  <si>
-    <t>136715558</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 13.02.2026</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 13.02.2026</t>
   </si>
 </sst>
 </file>
@@ -510,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -541,224 +475,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -776,31 +519,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B717157-AADE-4D1C-8386-742BAC89484E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="17">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,36 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136571711</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 19.02.2026</t>
+  </si>
+  <si>
+    <t>136567030</t>
+  </si>
+  <si>
+    <t>136722949</t>
+  </si>
+  <si>
+    <t>136721158</t>
+  </si>
+  <si>
+    <t>136567066</t>
+  </si>
+  <si>
+    <t>136702241</t>
+  </si>
+  <si>
+    <t>136731345</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 19.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +474,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,33 +505,122 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,31 +638,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F73339E-C2F1-4281-B642-327C6A17C2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,27 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>136697381</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 23.02.2026</t>
+  </si>
+  <si>
+    <t>136785258</t>
+  </si>
+  <si>
+    <t>136750040</t>
+  </si>
+  <si>
+    <t>136758521</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 23.02.2026</t>
   </si>
 </sst>
 </file>
@@ -444,7 +465,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,33 +496,71 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,31 +578,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F73339E-C2F1-4281-B642-327C6A17C2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89992BA1-FD45-44C2-8717-3B748B0D8B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,25 +51,31 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>136697381</t>
+    <t>136730434</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 23.02.2026</t>
-  </si>
-  <si>
-    <t>136785258</t>
-  </si>
-  <si>
-    <t>136750040</t>
-  </si>
-  <si>
-    <t>136758521</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 23.02.2026</t>
+    <t>Relatório de Recusa MDS 24.02.2026</t>
+  </si>
+  <si>
+    <t>136735734</t>
+  </si>
+  <si>
+    <t>136723883</t>
+  </si>
+  <si>
+    <t>136725389</t>
+  </si>
+  <si>
+    <t>136794705</t>
+  </si>
+  <si>
+    <t>136747614</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 24.02.2026</t>
   </si>
 </sst>
 </file>
@@ -465,7 +471,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -506,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -524,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -541,7 +547,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -558,9 +564,60 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89992BA1-FD45-44C2-8717-3B748B0D8B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,33 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>136730434</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa MDS 24.02.2026</t>
-  </si>
-  <si>
-    <t>136735734</t>
-  </si>
-  <si>
-    <t>136723883</t>
-  </si>
-  <si>
-    <t>136725389</t>
-  </si>
-  <si>
-    <t>136794705</t>
-  </si>
-  <si>
-    <t>136747614</t>
-  </si>
-  <si>
-    <t>RECUSA MDS 24.02.2026</t>
   </si>
 </sst>
 </file>
@@ -471,7 +444,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -502,122 +475,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -635,31 +519,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{53C29861-9674-4AA9-AD93-32136627C522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A4AEDB-4D7E-4DC2-9335-352191ADDDF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EB5F38-0258-4696-94E9-E9B59159741D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,30 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 26.02.2026</t>
+  </si>
+  <si>
+    <t>136735812</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 26.02.2026</t>
+  </si>
+  <si>
+    <t>136729959</t>
+  </si>
+  <si>
+    <t>136893750</t>
+  </si>
+  <si>
+    <t>136896144</t>
+  </si>
+  <si>
+    <t>136810335</t>
   </si>
 </sst>
 </file>
@@ -444,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -475,33 +499,88 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -519,31 +598,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_RECUSA_MDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EB5F38-0258-4696-94E9-E9B59159741D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE2A506-219C-49AF-8D7A-29410D02571B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,28 +51,25 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>RECUSA MDS 26.02.2026</t>
-  </si>
-  <si>
-    <t>136735812</t>
+    <t>135620708</t>
   </si>
   <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 26.02.2026</t>
-  </si>
-  <si>
-    <t>136729959</t>
-  </si>
-  <si>
-    <t>136893750</t>
-  </si>
-  <si>
-    <t>136896144</t>
-  </si>
-  <si>
-    <t>136810335</t>
+    <t>Relatório de Recusa MDS 29.11.2025</t>
+  </si>
+  <si>
+    <t>136898948</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa MDS 28.02.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 28.02.2026</t>
+  </si>
+  <si>
+    <t>RECUSA MDS 29.02.2026</t>
   </si>
 </sst>
 </file>
@@ -134,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -149,6 +146,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -468,7 +468,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -500,16 +500,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
+      <c r="D2" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -518,69 +518,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -598,31 +547,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>